--- a/outputs/daily/hr_rankings_2026-10-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-18.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>31.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2447,24 +2447,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -2477,26 +2477,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.1</v>
+        <v>44.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,26 +2510,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>31.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2619,102 +2619,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2765,24 +2765,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -2795,26 +2795,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,26 +2828,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.6</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
         <v>31.6</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>54.9</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2907,27 +2907,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2937,102 +2937,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,24 +4037,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4067,26 +4067,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.3</v>
+        <v>36.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,26 +4100,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>31.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4179,27 +4179,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,102 +4209,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4355,24 +4355,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4385,26 +4385,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,26 +4418,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R13" t="n">
         <v>31.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -4497,27 +4497,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,102 +4527,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>32.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,11 +5054,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.8</v>
+        <v>23.3</v>
       </c>
       <c r="Q15" t="n">
         <v>21.5</v>
@@ -5067,13 +5067,13 @@
         <v>31.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>0.8</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5086,12 +5086,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,67 +5163,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,24 +5309,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -5339,26 +5339,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5376,22 +5376,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
         <v>31.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>18.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -5451,27 +5451,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,102 +5481,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5627,24 +5627,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -5657,26 +5657,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.6</v>
+        <v>30.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,26 +5690,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>31.6</v>
       </c>
       <c r="S17" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5799,102 +5799,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -6021,13 +6021,13 @@
         <v>31.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6040,12 +6040,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -6117,67 +6117,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>31.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8619,24 +8619,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -8649,26 +8649,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.1</v>
+        <v>44.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,26 +8682,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>31.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8791,102 +8791,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8937,24 +8937,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -8967,26 +8967,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,26 +9000,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.6</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
         <v>31.6</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>54.9</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9032,12 +9032,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -9079,27 +9079,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9109,102 +9109,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10209,24 +10209,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -10239,26 +10239,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.3</v>
+        <v>36.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,26 +10272,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>31.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -10351,27 +10351,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10381,102 +10381,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10527,24 +10527,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -10557,26 +10557,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,26 +10590,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R13" t="n">
         <v>31.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10622,12 +10622,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -10669,27 +10669,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,102 +10699,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>32.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,11 +11226,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.8</v>
+        <v>23.3</v>
       </c>
       <c r="Q15" t="n">
         <v>21.5</v>
@@ -11239,13 +11239,13 @@
         <v>31.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>0.8</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11258,12 +11258,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,67 +11335,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,24 +11481,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -11511,26 +11511,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11548,22 +11548,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
         <v>31.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>18.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11576,12 +11576,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -11623,27 +11623,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,102 +11653,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11799,24 +11799,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -11829,26 +11829,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.6</v>
+        <v>30.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,26 +11862,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>31.6</v>
       </c>
       <c r="S17" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11894,12 +11894,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11971,102 +11971,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -12193,13 +12193,13 @@
         <v>31.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12212,12 +12212,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -12289,67 +12289,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-18.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>31.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -907,39 +907,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1200,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1224,7 +1220,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1251,7 +1247,7 @@
         <v>31.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1265,39 +1261,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1442,7 +1434,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1518,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1542,7 +1534,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>46.5</v>
+        <v>47.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1556,7 +1548,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1569,7 +1561,7 @@
         <v>31.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1583,39 +1575,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1760,7 +1748,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1836,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1860,7 +1848,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.8</v>
+        <v>46.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1874,7 +1862,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1887,7 +1875,7 @@
         <v>31.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1901,39 +1889,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2078,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2129,12 +2113,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2154,12 +2138,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2178,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.3</v>
+        <v>45.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2192,11 +2176,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
@@ -2205,13 +2189,13 @@
         <v>31.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2219,39 +2203,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2271,12 +2251,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2286,7 +2266,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2301,67 +2281,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2396,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2447,12 +2427,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2472,12 +2452,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2496,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.2</v>
+        <v>44.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,11 +2490,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>21.5</v>
@@ -2523,13 +2503,13 @@
         <v>31.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2537,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2589,12 +2565,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2604,7 +2580,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2619,67 +2595,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2714,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2790,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2814,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.1</v>
+        <v>43.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,7 +2804,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2841,7 +2817,7 @@
         <v>31.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2855,39 +2831,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3032,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3088,7 +3060,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3108,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3132,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.6</v>
+        <v>42.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3118,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3159,7 +3131,7 @@
         <v>31.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -3173,39 +3145,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3426,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3450,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>40.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3432,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3445,7 @@
         <v>31.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3491,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3668,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3744,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3768,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>37.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,7 +3746,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3795,7 +3759,7 @@
         <v>31.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3809,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3986,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,24 +3997,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4062,31 +4022,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.4</v>
+        <v>36</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,26 +4060,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
         <v>31.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4127,39 +4087,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4179,27 +4135,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,102 +4165,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4355,24 +4311,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4380,31 +4336,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,26 +4374,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R13" t="n">
         <v>31.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4445,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4497,27 +4449,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,102 +4479,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4698,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4722,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,7 +4688,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4749,7 +4701,7 @@
         <v>31.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4763,39 +4715,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4940,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,24 +4939,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -5016,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5026,21 +4974,21 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.1</v>
+        <v>31.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,26 +5002,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
         <v>31.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5081,39 +5029,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,12 +5077,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5148,12 +5092,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,102 +5107,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,12 +5253,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5334,12 +5278,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.4</v>
+        <v>29.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,11 +5316,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -5385,13 +5329,13 @@
         <v>31.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5399,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5456,17 +5396,17 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -5481,67 +5421,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5576,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5627,24 +5567,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -5652,31 +5592,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.7</v>
+        <v>28.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,26 +5630,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
         <v>31.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5717,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5769,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5784,12 +5720,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5799,102 +5735,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,12 +5881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5970,12 +5906,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.8</v>
+        <v>28.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,11 +5944,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -6021,13 +5957,13 @@
         <v>31.6</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6092,7 +6024,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,7 +6034,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -6117,67 +6049,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6212,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6288,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6312,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6326,7 +6258,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -6339,7 +6271,7 @@
         <v>31.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -6353,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6530,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,12 +6940,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +6991,7 @@
         <v>31.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -7079,39 +7007,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7256,7 +7180,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7372,7 +7296,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7396,7 +7320,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7410,7 +7334,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7423,7 +7347,7 @@
         <v>31.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7437,39 +7361,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7614,7 +7534,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7690,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7714,7 +7634,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>46.5</v>
+        <v>47.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7728,7 +7648,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7741,7 +7661,7 @@
         <v>31.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -7755,39 +7675,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7932,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8008,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8032,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.8</v>
+        <v>46.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8046,7 +7962,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8059,7 +7975,7 @@
         <v>31.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -8073,39 +7989,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8250,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8301,12 +8213,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8326,12 +8238,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8350,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.3</v>
+        <v>45.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8364,11 +8276,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
@@ -8377,13 +8289,13 @@
         <v>31.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8391,39 +8303,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,12 +8351,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -8458,7 +8366,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -8473,67 +8381,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8568,7 +8476,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8619,12 +8527,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8644,12 +8552,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8668,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.2</v>
+        <v>44.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,11 +8590,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>21.5</v>
@@ -8695,13 +8603,13 @@
         <v>31.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8709,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8761,12 +8665,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8776,7 +8680,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -8791,67 +8695,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8886,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8962,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8986,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.1</v>
+        <v>43.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,7 +8904,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -9013,7 +8917,7 @@
         <v>31.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -9027,39 +8931,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9204,7 +9104,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9260,7 +9160,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9280,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9304,7 +9204,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.6</v>
+        <v>42.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,7 +9218,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9331,7 +9231,7 @@
         <v>31.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -9345,39 +9245,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9522,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9598,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9622,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>40.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9532,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9545,7 @@
         <v>31.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -9663,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9840,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9916,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9940,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>37.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,7 +9846,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9967,7 +9859,7 @@
         <v>31.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -9981,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10158,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10209,24 +10097,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -10234,31 +10122,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.4</v>
+        <v>36</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,26 +10160,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
         <v>31.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10299,39 +10187,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10351,27 +10235,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10381,102 +10265,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10527,24 +10411,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -10552,31 +10436,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,26 +10474,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R13" t="n">
         <v>31.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10617,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10669,27 +10549,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,102 +10579,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10870,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10894,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,7 +10788,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10921,7 +10801,7 @@
         <v>31.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -10935,39 +10815,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11112,7 +10988,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,24 +11039,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -11188,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11198,21 +11074,21 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.1</v>
+        <v>31.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,26 +11102,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
         <v>31.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11253,39 +11129,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,12 +11177,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11320,12 +11192,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,102 +11207,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,12 +11353,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11506,12 +11378,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11530,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.4</v>
+        <v>29.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,11 +11416,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -11557,13 +11429,13 @@
         <v>31.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11571,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11628,17 +11496,17 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -11653,67 +11521,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11748,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11799,24 +11667,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -11824,31 +11692,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.7</v>
+        <v>28.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,26 +11730,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
         <v>31.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11889,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11941,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11956,12 +11820,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11971,102 +11835,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,12 +11981,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12142,12 +12006,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.8</v>
+        <v>28.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,11 +12044,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -12193,13 +12057,13 @@
         <v>31.6</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12264,7 +12124,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,7 +12134,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -12289,67 +12149,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12384,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12460,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12484,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12498,7 +12358,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -12511,7 +12371,7 @@
         <v>31.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -12525,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12702,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-18.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
